--- a/tabulka-radost.xlsx
+++ b/tabulka-radost.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kajik BP web\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kajik BP web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110C6F5B-4ED6-47EB-A0F2-C306D77F2585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB643D94-436C-4EE3-8E91-060AE299C4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26355" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{F919D72D-6EEA-46E4-BD17-FBF57A672A1B}"/>
+    <workbookView xWindow="-24465" yWindow="3975" windowWidth="21600" windowHeight="11385" xr2:uid="{F919D72D-6EEA-46E4-BD17-FBF57A672A1B}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -41,21 +41,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
-    <t>Mám/- se/. do/. bře/.</t>
-  </si>
-  <si>
-    <t>Dnes/. je/. krá/- sný/- den/.</t>
-  </si>
-  <si>
     <t>Ven/. ku/. sví/- tí/- slun/. ce/.</t>
   </si>
   <si>
     <t>Jsem/. šťast/. ný/-</t>
   </si>
   <si>
-    <t>Us/. mí/- vám/- se/. ce/. lý/- den/.</t>
-  </si>
-  <si>
     <t>Ahoj</t>
   </si>
   <si>
@@ -293,6 +284,15 @@
   </si>
   <si>
     <t>Mám/- tě/. rád/-</t>
+  </si>
+  <si>
+    <t>Mám/- se/. dob/. ře/.</t>
+  </si>
+  <si>
+    <t>Dnes/. je/. krás/- ný/- den/.</t>
+  </si>
+  <si>
+    <t>U/. smí/- vám/- se/. ce/. lý/- den/.</t>
   </si>
 </sst>
 </file>
@@ -690,82 +690,82 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
